--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484676_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484676_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8889</v>
+        <v>4.0958</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0683</v>
+        <v>3.0027</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8206</v>
+        <v>1.0931</v>
       </c>
       <c r="G2" t="n">
         <v>0.4201</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4971</v>
+        <v>0.7098</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7722</v>
+        <v>0.1622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2752</v>
+        <v>0.5477</v>
       </c>
       <c r="V2" t="n">
         <v>2.2328</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1968</v>
+        <v>1.9613</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1334</v>
+        <v>3.3134</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0634</v>
+        <v>-1.352</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0272</v>
+        <v>1.908</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07240000000000001</v>
+        <v>-1.7335</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0452</v>
+        <v>3.6416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2535</v>
+        <v>3.859</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1701</v>
+        <v>-0.1675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0833</v>
+        <v>4.0265</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2262</v>
+        <v>-1.951</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0977</v>
+        <v>-1.5661</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1285</v>
+        <v>-0.3849</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8188</v>
+        <v>0.2653</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0136</v>
+        <v>0.0487</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8052</v>
+        <v>0.2166</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6335</v>
+        <v>-0.945</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3011</v>
+        <v>0.3219</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9346</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4334</v>
+        <v>1.6698</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8597</v>
+        <v>2.1207</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4263</v>
+        <v>-0.4509</v>
       </c>
       <c r="G4" t="n">
-        <v>1.908</v>
+        <v>-1.3042</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7335</v>
+        <v>-3.1894</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6416</v>
+        <v>1.8852</v>
       </c>
       <c r="J4" t="n">
-        <v>3.859</v>
+        <v>1.2406</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1675</v>
+        <v>-1.4462</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0265</v>
+        <v>2.6868</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.951</v>
+        <v>-2.5448</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5661</v>
+        <v>-1.7431</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3849</v>
+        <v>-0.8017</v>
       </c>
       <c r="P4" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2627</v>
+        <v>-0.4267</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.405</v>
+        <v>-0.3869</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1423</v>
+        <v>-0.0398</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.945</v>
+        <v>1.5681</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.267</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3088</v>
+        <v>0.5991</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1313</v>
+        <v>-1.0747</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8225</v>
+        <v>1.6738</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3042</v>
+        <v>0.3324</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.1894</v>
+        <v>-0.8052</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8852</v>
+        <v>1.1376</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2406</v>
+        <v>0.0626</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4462</v>
+        <v>-0.1458</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6868</v>
+        <v>0.2084</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5448</v>
+        <v>0.2698</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7431</v>
+        <v>-0.6594</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8017</v>
+        <v>0.9293</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8326</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7877</v>
+        <v>0.0102</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3763</v>
+        <v>-0.221</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4114</v>
+        <v>0.2311</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5681</v>
+        <v>0.6231</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3011</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. SORIANO INCHAURRAGA</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1404</v>
+        <v>0.3225</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8181</v>
+        <v>-1.295</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6777</v>
+        <v>1.6175</v>
       </c>
       <c r="G6" t="n">
-        <v>0.648</v>
+        <v>0.0272</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0669</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7148</v>
+        <v>-0.0452</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3136</v>
+        <v>0.2535</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0217</v>
+        <v>0.1701</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2919</v>
+        <v>0.0833</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6656</v>
+        <v>-0.2262</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0885</v>
+        <v>-0.0977</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.1285</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.733</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5474</v>
+        <v>0.9446</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4208</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1266</v>
+        <v>0.3593</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3219</v>
+        <v>0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3219</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>V. SORIANO INCHAURRAGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0989</v>
+        <v>-0.0271</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6244</v>
+        <v>0.6258</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7234</v>
+        <v>-0.6529</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3324</v>
+        <v>0.648</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8052</v>
+        <v>-0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1376</v>
+        <v>0.7148</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0626</v>
+        <v>1.3136</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1458</v>
+        <v>0.0217</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2084</v>
+        <v>1.2919</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2698</v>
+        <v>-0.6656</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6594</v>
+        <v>-0.0885</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9293</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4901</v>
+        <v>0.3799</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.2285</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2807</v>
+        <v>0.1514</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0329</v>
+        <v>-1.5697</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6005</v>
+        <v>0.5588</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6334</v>
+        <v>-2.1285</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.1571</v>
+        <v>-1.6585</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1343</v>
+        <v>1.3452</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0228</v>
+        <v>-3.0037</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5713</v>
+        <v>0.1875</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0811</v>
+        <v>1.2354</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4902</v>
+        <v>-1.0479</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5858</v>
+        <v>-1.846</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0532</v>
+        <v>0.1098</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5326</v>
+        <v>-1.9558</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>3.0588</v>
+        <v>0.9893</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1222</v>
+        <v>0.6437</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9366</v>
+        <v>0.3456</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9658</v>
+        <v>-1.267</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9658</v>
+        <v>0.6439</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9626</v>
+        <v>-1.6438</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3156</v>
+        <v>-0.9721</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.647</v>
+        <v>-0.6718</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6052</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.4116</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0565</v>
+        <v>0.287</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1494</v>
+        <v>0.1246</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4037</v>
+        <v>-1.9017</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9905</v>
+        <v>-0.7728</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4132</v>
+        <v>-1.1288</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1576</v>
+        <v>-5.1571</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3306</v>
+        <v>-2.1343</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.827</v>
+        <v>-3.0228</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3103</v>
+        <v>-1.5713</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8111</v>
+        <v>-1.0811</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1214</v>
+        <v>-0.4902</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8474</v>
+        <v>-3.5858</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1418</v>
+        <v>-1.0532</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7056</v>
+        <v>-2.5326</v>
       </c>
       <c r="P10" t="n">
         <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6913</v>
+        <v>1.1901</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6802</v>
+        <v>0.7489</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0111</v>
+        <v>0.4412</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6543</v>
+        <v>0.9658</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.9658</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8727</v>
+        <v>-2.0512</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4717</v>
+        <v>-0.8114</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.401</v>
+        <v>-1.2398</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6585</v>
+        <v>-2.1576</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3452</v>
+        <v>-0.3306</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0037</v>
+        <v>-1.827</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1875</v>
+        <v>-0.3103</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2354</v>
+        <v>0.8111</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0479</v>
+        <v>-1.1214</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.846</v>
+        <v>-1.8474</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1098</v>
+        <v>-1.1418</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9558</v>
+        <v>-0.7056</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3138</v>
+        <v>-0.3388</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3869</v>
+        <v>-0.5011</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0731</v>
+        <v>0.1623</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.267</v>
+        <v>-0.6543</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9109</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.645</v>
+        <v>-3.6532</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2627</v>
+        <v>-1.0975</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3823</v>
+        <v>-2.5557</v>
       </c>
       <c r="G12" t="n">
         <v>-5.518</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2217</v>
+        <v>-0.0565</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3067</v>
+        <v>0.1333</v>
       </c>
       <c r="V12" t="n">
         <v>0.3219</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8497</v>
+        <v>-2.198199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9464</v>
+        <v>3.5979</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.795999999999999</v>
+        <v>-5.796</v>
       </c>
       <c r="G13" t="n">
         <v>-15.0649</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.692300000000001</v>
+        <v>-7.692299999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-7.3726</v>
@@ -1468,16 +1468,16 @@
         <v>13.7444</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5601</v>
+        <v>4.212</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1129000000000008</v>
+        <v>1.5387</v>
       </c>
       <c r="U13" t="n">
         <v>2.6733</v>
       </c>
       <c r="V13" t="n">
-        <v>3.156999999999999</v>
+        <v>3.157</v>
       </c>
       <c r="W13" t="n">
         <v>5.4626</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8103</v>
+        <v>3.5291</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4509</v>
+        <v>3.0663</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3594</v>
+        <v>0.4628</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2473</v>
@@ -1546,13 +1546,13 @@
         <v>0.1833</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7173</v>
+        <v>0.4361</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3107</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4065</v>
+        <v>0.51</v>
       </c>
       <c r="V14" t="n">
         <v>3.157</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9954</v>
+        <v>2.8279</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3354</v>
+        <v>1.143</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6601</v>
+        <v>1.6848</v>
       </c>
       <c r="G15" t="n">
         <v>2.8972</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0197</v>
+        <v>-0.1872</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0746</v>
+        <v>-0.267</v>
       </c>
       <c r="U15" t="n">
-        <v>0.055</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.3011</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1474</v>
+        <v>1.5753</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4766</v>
+        <v>1.5753</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6708</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5953</v>
+        <v>1.5753</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7042</v>
+        <v>0.3251</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8911</v>
+        <v>1.2502</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2829</v>
+        <v>1.5753</v>
       </c>
       <c r="K16" t="n">
-        <v>1.263</v>
+        <v>0.3251</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0199</v>
+        <v>1.2502</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6876</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5588</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1288</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.008</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9004</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8924</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5753</v>
+        <v>1.5295</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5753</v>
+        <v>0.5728</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.9567</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5753</v>
+        <v>1.5953</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3251</v>
+        <v>0.7042</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2502</v>
+        <v>0.8911</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5753</v>
+        <v>2.2829</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3251</v>
+        <v>1.263</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2502</v>
+        <v>1.0199</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.6876</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.5588</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.1288</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.626</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.8043</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.1783</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5506</v>
+        <v>1.1771</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2978</v>
+        <v>0.8747</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2528</v>
+        <v>0.3023</v>
       </c>
       <c r="G18" t="n">
         <v>1.5439</v>
@@ -1858,13 +1858,13 @@
         <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8101</v>
+        <v>-0.1836</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.3409</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1077</v>
+        <v>0.1572</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3261</v>
+        <v>0.6773</v>
       </c>
       <c r="E19" t="n">
         <v>0.4206</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0945</v>
+        <v>0.2567</v>
       </c>
       <c r="G19" t="n">
         <v>3.7855</v>
@@ -1936,13 +1936,13 @@
         <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0429</v>
+        <v>-0.6917</v>
       </c>
       <c r="T19" t="n">
         <v>-0.405</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.638</v>
+        <v>-0.2868</v>
       </c>
       <c r="V19" t="n">
         <v>0.3324</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2918</v>
+        <v>-0.1199</v>
       </c>
       <c r="E20" t="n">
-        <v>0.443</v>
+        <v>0.6353</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7348</v>
+        <v>-0.7553</v>
       </c>
       <c r="G20" t="n">
         <v>0.5313</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0614</v>
+        <v>0.1105</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.552</v>
+        <v>-0.3597</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4906</v>
+        <v>0.4702</v>
       </c>
       <c r="V20" t="n">
         <v>-0.945</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8971</v>
+        <v>-0.4279</v>
       </c>
       <c r="E21" t="n">
-        <v>0.121</v>
+        <v>0.3133</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0181</v>
+        <v>-0.7412</v>
       </c>
       <c r="G21" t="n">
         <v>2.2775</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4861</v>
+        <v>-0.017</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4955</v>
+        <v>-0.3032</v>
       </c>
       <c r="U21" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5889</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2455</v>
+        <v>-0.8491</v>
       </c>
       <c r="E22" t="n">
         <v>-0.6512</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.1979</v>
       </c>
       <c r="G22" t="n">
         <v>2.1638</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9823</v>
+        <v>-0.586</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2767</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7056</v>
+        <v>-0.3092</v>
       </c>
       <c r="V22" t="n">
         <v>0.3219</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4701</v>
+        <v>-1.0242</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5433</v>
+        <v>-0.7781</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0134</v>
+        <v>-0.2461</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2532</v>
+        <v>0.6445</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2564</v>
+        <v>0.2726</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.3719</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0674</v>
+        <v>-0.091</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.4985</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0674</v>
+        <v>-0.5895</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3207</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2564</v>
+        <v>-0.2259</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5770999999999999</v>
+        <v>0.9614</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1888</v>
+        <v>-0.3571</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4759</v>
+        <v>-0.0927</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2871</v>
+        <v>-0.2643</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5889</v>
+        <v>-0.945</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5889</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5574</v>
+        <v>-1.9291</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1627</v>
+        <v>0.1587</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3947</v>
+        <v>-2.0878</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6445</v>
+        <v>-0.2532</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2726</v>
+        <v>0.2564</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3719</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.091</v>
+        <v>0.0674</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4985</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5895</v>
+        <v>0.0674</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7354000000000001</v>
+        <v>-0.3207</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2259</v>
+        <v>0.2564</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9614</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8903</v>
+        <v>-0.2702</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4774</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.413</v>
+        <v>-0.3614</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.945</v>
+        <v>-1.5889</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.267</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0935</v>
+        <v>-2.4752</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0539</v>
+        <v>-1.5346</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0396</v>
+        <v>-0.9405</v>
       </c>
       <c r="G25" t="n">
         <v>-1.4491</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8345</v>
+        <v>0.4529</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6395</v>
+        <v>0.1588</v>
       </c>
       <c r="U25" t="n">
-        <v>0.195</v>
+        <v>0.2941</v>
       </c>
       <c r="V25" t="n">
         <v>-2.212</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.849699999999999</v>
+        <v>4.490799999999999</v>
       </c>
       <c r="E26" t="n">
         <v>5.796099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9463</v>
+        <v>-1.3055</v>
       </c>
       <c r="G26" t="n">
         <v>15.0647</v>
       </c>
       <c r="H26" t="n">
-        <v>7.6924</v>
+        <v>7.692399999999998</v>
       </c>
       <c r="I26" t="n">
         <v>7.372599999999999</v>
@@ -2482,13 +2482,13 @@
         <v>8.246600000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.5602</v>
+        <v>-1.9193</v>
       </c>
       <c r="T26" t="n">
         <v>-2.6733</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1127999999999999</v>
+        <v>0.7540000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-3.157</v>
